--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fyy95\Documents\courses\ECE1508\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wwr01\Point-Cloud-Classification-Using-PointNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94F52DF-2651-4265-AACF-9E59527D9008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D02A4F6-2F61-4F62-BE2D-D74E5F96DF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-5870" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pointnet" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>Scenario</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Instance Accuracy</t>
   </si>
@@ -108,32 +105,115 @@
   </si>
   <si>
     <t>dropout+jitter+normals+height+radius+pca+curvature+density</t>
+  </si>
+  <si>
+    <t>PointNet Scenario</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointNet++ Scenario</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rotation along random axis</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jitter+(sigmga = 0.01, clip = 0.05)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Height</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Radius</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCA</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Curvature</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Density</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noramls + Height</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter + Radius</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter + Height</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter + Normals</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter + Height + Normals</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter + Density + Normals</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter + Height + Radius + Normals</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Scale + Shift</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Scale + Shift + Jitter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dropout + Jitter (With Optimization)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -455,36 +535,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="63.109375" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="63.125" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="5" width="50.109375" customWidth="1"/>
+    <col min="4" max="4" width="45.625" customWidth="1"/>
+    <col min="5" max="5" width="50.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <v>0.87943499999999997</v>
@@ -501,9 +581,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>0.82903199999999999</v>
@@ -520,9 +600,9 @@
         <v>-5.0402999999999976E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>0.87137100000000001</v>
@@ -539,9 +619,9 @@
         <v>-5.6650000000000311E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>0.875</v>
@@ -558,9 +638,9 @@
         <v>-4.4349999999999667E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>0.87580599999999997</v>
@@ -577,9 +657,9 @@
         <v>-6.2429999999999986E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>0.88871</v>
@@ -596,9 +676,9 @@
         <v>9.2750000000000332E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0.88709700000000002</v>
@@ -615,9 +695,9 @@
         <v>8.4429999999999783E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>0.87056500000000003</v>
@@ -634,9 +714,9 @@
         <v>-1.487000000000005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1">
         <v>0.89072600000000002</v>
@@ -649,13 +729,13 @@
         <v>1.1291000000000051E-2</v>
       </c>
       <c r="E10" s="1">
-        <f t="shared" ref="E10:E20" si="7">C10-$C$2</f>
+        <f t="shared" ref="E10" si="7">C10-$C$2</f>
         <v>1.4148000000000049E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>0.89032299999999998</v>
@@ -672,9 +752,9 @@
         <v>1.0888000000000009E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0.88871</v>
@@ -691,9 +771,9 @@
         <v>6.333000000000033E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1">
         <v>0.90645200000000004</v>
@@ -706,13 +786,13 @@
         <v>2.7017000000000069E-2</v>
       </c>
       <c r="E13" s="1">
-        <f t="shared" ref="E13:E20" si="10">D13-$D$2</f>
+        <f t="shared" ref="E13" si="10">D13-$D$2</f>
         <v>2.7017000000000069E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0.910887</v>
@@ -725,13 +805,13 @@
         <v>3.1452000000000035E-2</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14:E20" si="11">C14-$C$2</f>
+        <f t="shared" ref="E14" si="11">C14-$C$2</f>
         <v>4.263399999999995E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>0.914516</v>
@@ -744,13 +824,13 @@
         <v>3.5081000000000029E-2</v>
       </c>
       <c r="E15">
-        <f t="shared" ref="E15:E20" si="12">D15-$D$2</f>
+        <f t="shared" ref="E15" si="12">D15-$D$2</f>
         <v>3.5081000000000029E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1">
         <v>0.91693500000000006</v>
@@ -763,13 +843,13 @@
         <v>3.7500000000000089E-2</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" ref="E16:E20" si="13">C16-$C$2</f>
+        <f t="shared" ref="E16:E18" si="13">C16-$C$2</f>
         <v>5.6699999999999973E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>0.910887</v>
@@ -786,9 +866,9 @@
         <v>3.8148999999999988E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>0.90806500000000001</v>
@@ -805,9 +885,9 @@
         <v>4.7938999999999954E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>0.91612899999999997</v>
@@ -824,9 +904,9 @@
         <v>3.6694000000000004E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>0.91612899999999997</v>
@@ -843,7 +923,338 @@
         <v>5.5632000000000015E-2</v>
       </c>
     </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.91391599999999995</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.88260300000000003</v>
+      </c>
+      <c r="D24" s="2">
+        <f>B24-$B$2</f>
+        <v>3.4480999999999984E-2</v>
+      </c>
+      <c r="E24" s="2">
+        <f>C24-$C$2</f>
+        <v>5.5250000000000021E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>0.89482200000000001</v>
+      </c>
+      <c r="C25">
+        <v>0.878467</v>
+      </c>
+      <c r="D25">
+        <f>B25-$B$2</f>
+        <v>1.538700000000004E-2</v>
+      </c>
+      <c r="E25">
+        <f>D25-$D$2</f>
+        <v>1.538700000000004E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>0.90622999999999998</v>
+      </c>
+      <c r="C26">
+        <v>0.88206300000000004</v>
+      </c>
+      <c r="D26">
+        <f>B26-$B$2</f>
+        <v>2.6795000000000013E-2</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ref="E26" si="15">C26-$C$2</f>
+        <v>5.4710000000000036E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>0.913188</v>
+      </c>
+      <c r="C27">
+        <v>0.88076100000000002</v>
+      </c>
+      <c r="D27">
+        <f t="shared" ref="D27:D31" si="16">B27-$B$2</f>
+        <v>3.3753000000000033E-2</v>
+      </c>
+      <c r="E27">
+        <f t="shared" ref="E27" si="17">D27-$D$2</f>
+        <v>3.3753000000000033E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>0.91836600000000002</v>
+      </c>
+      <c r="C28">
+        <v>0.88681200000000004</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="16"/>
+        <v>3.8931000000000049E-2</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ref="E28" si="18">C28-$C$2</f>
+        <v>5.945900000000004E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>0.91723299999999997</v>
+      </c>
+      <c r="C29">
+        <v>0.88156000000000001</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="16"/>
+        <v>3.7797999999999998E-2</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ref="E29" si="19">D29-$D$2</f>
+        <v>3.7797999999999998E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>0.91156999999999999</v>
+      </c>
+      <c r="C30">
+        <v>0.88656699999999999</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="16"/>
+        <v>3.2135000000000025E-2</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ref="E30" si="20">C30-$C$2</f>
+        <v>5.9213999999999989E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <v>0.91812300000000002</v>
+      </c>
+      <c r="C31">
+        <v>0.88875599999999999</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="16"/>
+        <v>3.8688000000000056E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32">
+        <v>0.907443</v>
+      </c>
+      <c r="C32">
+        <v>0.87873100000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33">
+        <v>0.90833299999999995</v>
+      </c>
+      <c r="C33">
+        <v>0.86588200000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34">
+        <v>0.91359199999999996</v>
+      </c>
+      <c r="C34">
+        <v>0.88029500000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35">
+        <v>0.90987099999999999</v>
+      </c>
+      <c r="C35">
+        <v>0.87909599999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36">
+        <v>0.91181199999999996</v>
+      </c>
+      <c r="C36">
+        <v>0.88713299999999995</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37">
+        <v>0.91068000000000005</v>
+      </c>
+      <c r="C37">
+        <v>0.87777899999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38">
+        <v>0.90687700000000004</v>
+      </c>
+      <c r="C38">
+        <v>0.876309</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39">
+        <v>0.90792899999999999</v>
+      </c>
+      <c r="C39">
+        <v>0.87090599999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40">
+        <v>0.92135900000000004</v>
+      </c>
+      <c r="C40">
+        <v>0.89281999999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41">
+        <v>0.91957900000000004</v>
+      </c>
+      <c r="C41">
+        <v>0.88603500000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42">
+        <v>0.91901299999999997</v>
+      </c>
+      <c r="C42">
+        <v>0.89135799999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43">
+        <v>0.91893199999999997</v>
+      </c>
+      <c r="C43">
+        <v>0.89242100000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44">
+        <v>0.91335</v>
+      </c>
+      <c r="C44">
+        <v>0.87372300000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45">
+        <v>0.90906100000000001</v>
+      </c>
+      <c r="C45">
+        <v>0.87926099999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46">
+        <v>0.92678000000000005</v>
+      </c>
+      <c r="C46">
+        <v>0.90144199999999997</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wwr01\Point-Cloud-Classification-Using-PointNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D02A4F6-2F61-4F62-BE2D-D74E5F96DF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9041242-62CB-4030-B820-DA44D6313DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -951,12 +951,12 @@
         <v>0.88260300000000003</v>
       </c>
       <c r="D24" s="2">
-        <f>B24-$B$2</f>
-        <v>3.4480999999999984E-2</v>
+        <f>B24-$B$24</f>
+        <v>0</v>
       </c>
       <c r="E24" s="2">
-        <f>C24-$C$2</f>
-        <v>5.5250000000000021E-2</v>
+        <f>C24-$C$24</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -970,12 +970,12 @@
         <v>0.878467</v>
       </c>
       <c r="D25">
-        <f>B25-$B$2</f>
-        <v>1.538700000000004E-2</v>
+        <f>B25-$B$24</f>
+        <v>-1.9093999999999944E-2</v>
       </c>
       <c r="E25">
-        <f>D25-$D$2</f>
-        <v>1.538700000000004E-2</v>
+        <f>C25-$C$24</f>
+        <v>-4.1360000000000285E-3</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -989,12 +989,12 @@
         <v>0.88206300000000004</v>
       </c>
       <c r="D26">
-        <f>B26-$B$2</f>
-        <v>2.6795000000000013E-2</v>
+        <f>B26-$B$24</f>
+        <v>-7.6859999999999706E-3</v>
       </c>
       <c r="E26">
-        <f t="shared" ref="E26" si="15">C26-$C$2</f>
-        <v>5.4710000000000036E-2</v>
+        <f>C26-$C$24</f>
+        <v>-5.3999999999998494E-4</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1008,12 +1008,12 @@
         <v>0.88076100000000002</v>
       </c>
       <c r="D27">
-        <f t="shared" ref="D27:D31" si="16">B27-$B$2</f>
-        <v>3.3753000000000033E-2</v>
+        <f>B27-$B$24</f>
+        <v>-7.2799999999995091E-4</v>
       </c>
       <c r="E27">
-        <f t="shared" ref="E27" si="17">D27-$D$2</f>
-        <v>3.3753000000000033E-2</v>
+        <f>C27-$C$24</f>
+        <v>-1.8420000000000103E-3</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1027,12 +1027,12 @@
         <v>0.88681200000000004</v>
       </c>
       <c r="D28">
-        <f t="shared" si="16"/>
-        <v>3.8931000000000049E-2</v>
+        <f>B28-$B$24</f>
+        <v>4.450000000000065E-3</v>
       </c>
       <c r="E28">
-        <f t="shared" ref="E28" si="18">C28-$C$2</f>
-        <v>5.945900000000004E-2</v>
+        <f>C28-$C$24</f>
+        <v>4.2090000000000183E-3</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1046,12 +1046,12 @@
         <v>0.88156000000000001</v>
       </c>
       <c r="D29">
-        <f t="shared" si="16"/>
-        <v>3.7797999999999998E-2</v>
+        <f>B29-$B$24</f>
+        <v>3.3170000000000144E-3</v>
       </c>
       <c r="E29">
-        <f t="shared" ref="E29" si="19">D29-$D$2</f>
-        <v>3.7797999999999998E-2</v>
+        <f>C29-$C$24</f>
+        <v>-1.0430000000000161E-3</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -1065,12 +1065,12 @@
         <v>0.88656699999999999</v>
       </c>
       <c r="D30">
-        <f t="shared" si="16"/>
-        <v>3.2135000000000025E-2</v>
+        <f>B30-$B$24</f>
+        <v>-2.3459999999999592E-3</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30" si="20">C30-$C$2</f>
-        <v>5.9213999999999989E-2</v>
+        <f>C30-$C$24</f>
+        <v>3.9639999999999675E-3</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -1084,8 +1084,12 @@
         <v>0.88875599999999999</v>
       </c>
       <c r="D31">
-        <f t="shared" si="16"/>
-        <v>3.8688000000000056E-2</v>
+        <f>B31-$B$24</f>
+        <v>4.2070000000000718E-3</v>
+      </c>
+      <c r="E31">
+        <f>C31-$C$24</f>
+        <v>6.1529999999999641E-3</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -1098,8 +1102,16 @@
       <c r="C32">
         <v>0.87873100000000004</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32">
+        <f>B32-$B$24</f>
+        <v>-6.472999999999951E-3</v>
+      </c>
+      <c r="E32">
+        <f>C32-$C$24</f>
+        <v>-3.8719999999999866E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1109,8 +1121,16 @@
       <c r="C33">
         <v>0.86588200000000004</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33">
+        <f>B33-$B$24</f>
+        <v>-5.5830000000000046E-3</v>
+      </c>
+      <c r="E33">
+        <f>C33-$C$24</f>
+        <v>-1.6720999999999986E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1120,8 +1140,16 @@
       <c r="C34">
         <v>0.88029500000000005</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <f>B34-$B$24</f>
+        <v>-3.2399999999999096E-4</v>
+      </c>
+      <c r="E34">
+        <f>C34-$C$24</f>
+        <v>-2.3079999999999767E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -1131,8 +1159,16 @@
       <c r="C35">
         <v>0.87909599999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <f>B35-$B$24</f>
+        <v>-4.0449999999999653E-3</v>
+      </c>
+      <c r="E35">
+        <f>C35-$C$24</f>
+        <v>-3.5070000000000379E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1142,8 +1178,16 @@
       <c r="C36">
         <v>0.88713299999999995</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36">
+        <f>B36-$B$24</f>
+        <v>-2.1039999999999948E-3</v>
+      </c>
+      <c r="E36">
+        <f>C36-$C$24</f>
+        <v>4.529999999999923E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -1153,8 +1197,16 @@
       <c r="C37">
         <v>0.87777899999999998</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37">
+        <f>B37-$B$24</f>
+        <v>-3.2359999999999056E-3</v>
+      </c>
+      <c r="E37">
+        <f>C37-$C$24</f>
+        <v>-4.8240000000000505E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -1164,8 +1216,16 @@
       <c r="C38">
         <v>0.876309</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38">
+        <f>B38-$B$24</f>
+        <v>-7.0389999999999064E-3</v>
+      </c>
+      <c r="E38">
+        <f>C38-$C$24</f>
+        <v>-6.2940000000000218E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -1175,8 +1235,16 @@
       <c r="C39">
         <v>0.87090599999999996</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39">
+        <f>B39-$B$24</f>
+        <v>-5.9869999999999646E-3</v>
+      </c>
+      <c r="E39">
+        <f>C39-$C$24</f>
+        <v>-1.1697000000000068E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -1186,8 +1254,16 @@
       <c r="C40">
         <v>0.89281999999999995</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <f>B40-$B$24</f>
+        <v>7.4430000000000884E-3</v>
+      </c>
+      <c r="E40">
+        <f>C40-$C$24</f>
+        <v>1.0216999999999921E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>36</v>
       </c>
@@ -1197,8 +1273,16 @@
       <c r="C41">
         <v>0.88603500000000002</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41">
+        <f>B41-$B$24</f>
+        <v>5.6630000000000846E-3</v>
+      </c>
+      <c r="E41">
+        <f>C41-$C$24</f>
+        <v>3.4319999999999906E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -1208,8 +1292,16 @@
       <c r="C42">
         <v>0.89135799999999998</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42">
+        <f>B42-$B$24</f>
+        <v>5.0970000000000182E-3</v>
+      </c>
+      <c r="E42">
+        <f>C42-$C$24</f>
+        <v>8.7549999999999573E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -1219,8 +1311,16 @@
       <c r="C43">
         <v>0.89242100000000002</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43">
+        <f>B43-$B$24</f>
+        <v>5.0160000000000204E-3</v>
+      </c>
+      <c r="E43">
+        <f>C43-$C$24</f>
+        <v>9.8179999999999934E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -1230,8 +1330,16 @@
       <c r="C44">
         <v>0.87372300000000003</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44">
+        <f>B44-$B$24</f>
+        <v>-5.6599999999995543E-4</v>
+      </c>
+      <c r="E44">
+        <f>C44-$C$24</f>
+        <v>-8.879999999999999E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -1241,8 +1349,16 @@
       <c r="C45">
         <v>0.87926099999999996</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45">
+        <f>B45-$B$24</f>
+        <v>-4.8549999999999427E-3</v>
+      </c>
+      <c r="E45">
+        <f>C45-$C$24</f>
+        <v>-3.3420000000000671E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>41</v>
       </c>
@@ -1251,6 +1367,14 @@
       </c>
       <c r="C46">
         <v>0.90144199999999997</v>
+      </c>
+      <c r="D46">
+        <f>B46-$B$24</f>
+        <v>1.2864000000000098E-2</v>
+      </c>
+      <c r="E46">
+        <f>C46-$C$24</f>
+        <v>1.8838999999999939E-2</v>
       </c>
     </row>
   </sheetData>
